--- a/4 курс/ФИТ/МОБ.xlsx
+++ b/4 курс/ФИТ/МОБ.xlsx
@@ -230,7 +230,7 @@
     <numFmt numFmtId="180" formatCode="0.000"/>
     <numFmt numFmtId="181" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -277,13 +277,6 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -783,152 +776,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -945,24 +938,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -978,9 +959,6 @@
     <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -999,9 +977,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1017,46 +992,25 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="180" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
@@ -1945,48 +1899,6 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>324485</xdr:colOff>
-      <xdr:row>125</xdr:row>
-      <xdr:rowOff>56515</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>299720</xdr:colOff>
-      <xdr:row>127</xdr:row>
-      <xdr:rowOff>142240</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="31" name="Изображение 30"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6072505" y="26291540"/>
-          <a:ext cx="2495550" cy="447675"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2322,23 +2234,23 @@
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="4">
         <v>888.43</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="4">
         <v>1098.54</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="4">
         <v>670.3</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="4">
         <v>474.142</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="6">
         <f>H5-F5-E5-C5-D5</f>
         <v>2754.708</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="4">
         <v>5886.12</v>
       </c>
     </row>
@@ -2346,23 +2258,23 @@
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="4">
         <v>1064.006</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="4">
         <v>1251.038</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="4">
         <v>664.096</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="4">
         <v>1614.72</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="6">
         <f>H6-F6-E6-C6-D6</f>
         <v>2719.54</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="4">
         <v>7313.4</v>
       </c>
     </row>
@@ -2370,23 +2282,23 @@
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="4">
         <v>446.834</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="4">
         <v>188.235</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="4">
         <v>1046.584</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="4">
         <v>1000.61</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="6">
         <f>H7-F7-E7-C7-D7</f>
         <v>2300.537</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="4">
         <v>4982.8</v>
       </c>
     </row>
@@ -2394,23 +2306,23 @@
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="4">
         <v>717.32</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="4">
         <v>989.254</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="4">
         <v>757.73</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="4">
         <v>393.541</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="6">
         <f>H8-F8-E8-C8-D8</f>
         <v>2148.355</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="4">
         <v>5006.2</v>
       </c>
     </row>
@@ -2418,114 +2330,114 @@
       <c r="B9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="4">
         <v>1001.423</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="4">
         <v>1470.213</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="4">
         <v>1050.223</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="4">
         <v>964.213</v>
       </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="9"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="6"/>
     </row>
     <row r="10" spans="2:8">
       <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="4">
         <v>472.8</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="4">
         <v>980.35</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="4">
         <v>232.68</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="4">
         <v>381.55</v>
       </c>
-      <c r="G10" s="8"/>
-      <c r="H10" s="9"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="6"/>
     </row>
     <row r="11" spans="2:8">
       <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="6">
         <f>C12-C13-C9-C10</f>
-        <v>2183.737</v>
-      </c>
-      <c r="D11" s="7">
+        <v>1295.307</v>
+      </c>
+      <c r="D11" s="6">
         <f>D12-D13-D9-D10</f>
-        <v>2434.31</v>
-      </c>
-      <c r="E11" s="7">
+        <v>1335.77</v>
+      </c>
+      <c r="E11" s="6">
         <f>E12-E13-E9-E10</f>
-        <v>1231.487</v>
-      </c>
-      <c r="F11" s="7">
+        <v>561.187</v>
+      </c>
+      <c r="F11" s="6">
         <f>F12-F13-F9-F10</f>
-        <v>651.566</v>
-      </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="9"/>
+        <v>177.423999999999</v>
+      </c>
+      <c r="G11" s="7"/>
+      <c r="H11" s="6"/>
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="6">
         <f>H5</f>
         <v>5886.12</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="6">
         <f>H6</f>
         <v>7313.4</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="6">
         <f>H7</f>
         <v>4982.8</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="6">
         <f>H8</f>
         <v>5006.2</v>
       </c>
-      <c r="G12" s="11"/>
-      <c r="H12" s="10"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="6"/>
     </row>
     <row r="13" spans="2:8">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="12">
-        <f>SUM(C6:C8)</f>
-        <v>2228.16</v>
-      </c>
-      <c r="D13" s="12">
-        <f>SUM(D6:D8)</f>
-        <v>2428.527</v>
-      </c>
-      <c r="E13" s="12">
-        <f>SUM(E6:E8)</f>
-        <v>2468.41</v>
-      </c>
-      <c r="F13" s="12">
-        <f>SUM(F6:F8)</f>
-        <v>3008.871</v>
-      </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
+      <c r="C13" s="8">
+        <f>SUM(C5:C8)</f>
+        <v>3116.59</v>
+      </c>
+      <c r="D13" s="8">
+        <f>SUM(D5:D8)</f>
+        <v>3527.067</v>
+      </c>
+      <c r="E13" s="8">
+        <f>SUM(E5:E8)</f>
+        <v>3138.71</v>
+      </c>
+      <c r="F13" s="8">
+        <f>SUM(F5:F8)</f>
+        <v>3483.013</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
     </row>
     <row r="14" ht="15" spans="1:4">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="15"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="11"/>
     </row>
     <row r="15" ht="15" spans="1:2">
       <c r="A15" s="2"/>
@@ -2540,130 +2452,130 @@
       <c r="A17" s="2"/>
     </row>
     <row r="18" ht="15" spans="1:1">
-      <c r="A18" s="13"/>
+      <c r="A18" s="9"/>
     </row>
     <row r="19" ht="15" spans="1:4">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="15"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="11"/>
     </row>
     <row r="20" ht="15" spans="1:4">
       <c r="A20" s="2"/>
-      <c r="D20" s="15"/>
+      <c r="D20" s="11"/>
     </row>
     <row r="21" ht="15" spans="1:3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
     </row>
     <row r="25" spans="2:2">
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="26" spans="2:5">
-      <c r="B26" s="16">
+      <c r="B26" s="12">
         <f>C5/$C$12</f>
         <v>0.15093644030363</v>
       </c>
-      <c r="C26" s="16">
+      <c r="C26" s="12">
         <f>D5/$D$12</f>
         <v>0.15020920502092</v>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="12">
         <f>E5/$E$12</f>
         <v>0.134522758288512</v>
       </c>
-      <c r="E26" s="16">
+      <c r="E26" s="12">
         <f>F5/$F$12</f>
         <v>0.0947109584115697</v>
       </c>
     </row>
     <row r="27" spans="2:5">
-      <c r="B27" s="16">
+      <c r="B27" s="12">
         <f>C6/$C$12</f>
         <v>0.180765257928822</v>
       </c>
-      <c r="C27" s="16">
+      <c r="C27" s="12">
         <f>D6/$D$12</f>
         <v>0.17106106598846</v>
       </c>
-      <c r="D27" s="16">
+      <c r="D27" s="12">
         <f>E6/$E$12</f>
         <v>0.133277675202697</v>
       </c>
-      <c r="E27" s="16">
+      <c r="E27" s="12">
         <f>F6/$F$12</f>
         <v>0.322544045383724</v>
       </c>
     </row>
     <row r="28" spans="2:5">
-      <c r="B28" s="16">
+      <c r="B28" s="12">
         <f>C7/$C$12</f>
         <v>0.0759131652090002</v>
       </c>
-      <c r="C28" s="16">
+      <c r="C28" s="12">
         <f>D7/$D$12</f>
         <v>0.0257383706620724</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="12">
         <f>E7/$E$12</f>
         <v>0.210039335313478</v>
       </c>
-      <c r="E28" s="16">
+      <c r="E28" s="12">
         <f>F7/$F$12</f>
         <v>0.199874156046502</v>
       </c>
     </row>
     <row r="29" spans="2:5">
-      <c r="B29" s="16">
+      <c r="B29" s="12">
         <f>C8/$C$12</f>
         <v>0.121866356785115</v>
       </c>
-      <c r="C29" s="16">
+      <c r="C29" s="12">
         <f>D8/$D$12</f>
         <v>0.135265950173654</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="12">
         <f>E8/$E$12</f>
         <v>0.152069117765112</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="12">
         <f>F8/$F$12</f>
         <v>0.0786107227038472</v>
       </c>
     </row>
     <row r="30" spans="2:5">
-      <c r="B30" s="17">
+      <c r="B30" s="12">
         <f>SUM(B26:B29)</f>
         <v>0.529481220226567</v>
       </c>
-      <c r="C30" s="17">
+      <c r="C30" s="12">
         <f>SUM(C26:C29)</f>
         <v>0.482274591845106</v>
       </c>
-      <c r="D30" s="17">
+      <c r="D30" s="12">
         <f>SUM(D26:D29)</f>
         <v>0.6299088865698</v>
       </c>
-      <c r="E30" s="17">
+      <c r="E30" s="12">
         <f>SUM(E26:E29)</f>
         <v>0.695739882545644</v>
       </c>
     </row>
     <row r="31" spans="7:10">
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="18"/>
-      <c r="J31" s="18"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
     </row>
     <row r="33" spans="3:3">
-      <c r="C33" s="18"/>
+      <c r="C33" s="13"/>
     </row>
     <row r="35" ht="25" customHeight="1" spans="1:2">
       <c r="A35" s="2"/>
-      <c r="B35" s="19"/>
+      <c r="B35" s="14"/>
     </row>
     <row r="36" ht="15" spans="1:2">
       <c r="A36" s="2"/>
@@ -2671,273 +2583,272 @@
     </row>
     <row r="37" ht="15" spans="1:2">
       <c r="A37" s="2"/>
-      <c r="B37" s="20" t="s">
+      <c r="B37" s="15" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="39" spans="2:4">
-      <c r="B39" s="21" t="s">
+      <c r="B39" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C39" s="21" t="s">
+      <c r="C39" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="D39" s="21" t="s">
+      <c r="D39" s="16" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="40" spans="2:4">
-      <c r="B40" s="21" t="s">
+      <c r="B40" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C40" s="22">
+      <c r="C40" s="17">
         <v>0.005</v>
       </c>
-      <c r="D40" s="21">
+      <c r="D40" s="16">
         <f>G5*(1+0.005)</f>
         <v>2768.48154</v>
       </c>
     </row>
     <row r="41" spans="2:4">
-      <c r="B41" s="21" t="s">
+      <c r="B41" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C41" s="22">
+      <c r="C41" s="17">
         <v>0.042</v>
       </c>
-      <c r="D41" s="21">
+      <c r="D41" s="16">
         <f>G6*(1+0.042)</f>
         <v>2833.76068</v>
       </c>
     </row>
     <row r="42" spans="2:4">
-      <c r="B42" s="21" t="s">
+      <c r="B42" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C42" s="22">
+      <c r="C42" s="17">
         <v>0.03</v>
       </c>
-      <c r="D42" s="21">
+      <c r="D42" s="16">
         <f>G7*(1+0.03)</f>
         <v>2369.55311</v>
       </c>
     </row>
     <row r="43" spans="2:4">
-      <c r="B43" s="21" t="s">
+      <c r="B43" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="22">
+      <c r="C43" s="17">
         <v>0.005</v>
       </c>
-      <c r="D43" s="21">
+      <c r="D43" s="16">
         <f>G8*(1+0.005)</f>
         <v>2159.096775</v>
       </c>
     </row>
     <row r="48" spans="2:10">
-      <c r="B48" s="21">
+      <c r="B48" s="16">
         <v>1</v>
       </c>
-      <c r="C48" s="21">
+      <c r="C48" s="16">
         <v>0</v>
       </c>
-      <c r="D48" s="21">
+      <c r="D48" s="16">
         <v>0</v>
       </c>
-      <c r="E48" s="23">
+      <c r="E48" s="18">
         <v>0</v>
       </c>
-      <c r="G48" s="16">
+      <c r="G48" s="12">
         <f>1-B26</f>
         <v>0.84906355969637</v>
       </c>
-      <c r="H48" s="16">
+      <c r="H48" s="12">
         <f>-C26</f>
         <v>-0.15020920502092</v>
       </c>
-      <c r="I48" s="16">
+      <c r="I48" s="12">
         <f>-D26</f>
         <v>-0.134522758288512</v>
       </c>
-      <c r="J48" s="16">
+      <c r="J48" s="12">
         <f>-E26</f>
         <v>-0.0947109584115697</v>
       </c>
     </row>
     <row r="49" spans="2:10">
-      <c r="B49" s="21">
+      <c r="B49" s="16">
         <v>0</v>
       </c>
-      <c r="C49" s="21">
+      <c r="C49" s="16">
         <v>1</v>
       </c>
-      <c r="D49" s="21">
+      <c r="D49" s="16">
         <v>0</v>
       </c>
-      <c r="E49" s="23">
+      <c r="E49" s="18">
         <v>0</v>
       </c>
-      <c r="G49" s="16">
+      <c r="G49" s="12">
         <f>-B27</f>
         <v>-0.180765257928822</v>
       </c>
-      <c r="H49" s="16">
+      <c r="H49" s="12">
         <f>1-C27</f>
         <v>0.828938934011541</v>
       </c>
-      <c r="I49" s="16">
+      <c r="I49" s="12">
         <f>-D27</f>
         <v>-0.133277675202697</v>
       </c>
-      <c r="J49" s="16">
+      <c r="J49" s="12">
         <f>-E27</f>
         <v>-0.322544045383724</v>
       </c>
     </row>
     <row r="50" ht="15" spans="2:17">
-      <c r="B50" s="21">
+      <c r="B50" s="16">
         <v>0</v>
       </c>
-      <c r="C50" s="21">
+      <c r="C50" s="16">
         <v>0</v>
       </c>
-      <c r="D50" s="21">
+      <c r="D50" s="16">
         <v>1</v>
       </c>
-      <c r="E50" s="23">
+      <c r="E50" s="18">
         <v>0</v>
       </c>
-      <c r="F50" s="44" t="s">
+      <c r="F50" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="G50" s="16">
+      <c r="G50" s="12">
         <f>-B28</f>
         <v>-0.0759131652090002</v>
       </c>
-      <c r="H50" s="16">
+      <c r="H50" s="12">
         <f>-C28</f>
         <v>-0.0257383706620724</v>
       </c>
-      <c r="I50" s="16">
+      <c r="I50" s="12">
         <f>1-D28</f>
         <v>0.789960664686522</v>
       </c>
-      <c r="J50" s="16">
+      <c r="J50" s="12">
         <f>-E28</f>
         <v>-0.199874156046502</v>
       </c>
-      <c r="Q50" s="18"/>
+      <c r="Q50" s="13"/>
     </row>
     <row r="51" spans="2:10">
-      <c r="B51" s="21">
+      <c r="B51" s="16">
         <v>0</v>
       </c>
-      <c r="C51" s="21">
+      <c r="C51" s="16">
         <v>0</v>
       </c>
-      <c r="D51" s="21">
+      <c r="D51" s="16">
         <v>0</v>
       </c>
-      <c r="E51" s="23">
+      <c r="E51" s="18">
         <v>1</v>
       </c>
-      <c r="G51" s="16">
+      <c r="G51" s="12">
         <f>-B29</f>
         <v>-0.121866356785115</v>
       </c>
-      <c r="H51" s="16">
+      <c r="H51" s="12">
         <f>-C29</f>
         <v>-0.135265950173654</v>
       </c>
-      <c r="I51" s="16">
+      <c r="I51" s="12">
         <f>-D29</f>
         <v>-0.152069117765112</v>
       </c>
-      <c r="J51" s="16">
+      <c r="J51" s="12">
         <f>1-E29</f>
         <v>0.921389277296153</v>
       </c>
     </row>
     <row r="53" spans="2:5">
-      <c r="B53" s="16" cm="1">
+      <c r="B53" s="12" cm="1">
         <f t="array" ref="B53:E56">MINVERSE(G48:J51)</f>
         <v>1.31654156788878</v>
       </c>
-      <c r="C53" s="16">
+      <c r="C53" s="12">
         <v>0.300054501413519</v>
       </c>
-      <c r="D53" s="16">
+      <c r="D53" s="12">
         <v>0.33508178430917</v>
       </c>
-      <c r="E53" s="16">
+      <c r="E53" s="12">
         <v>0.313055407044388</v>
       </c>
     </row>
     <row r="54" spans="2:5">
-      <c r="B54" s="16">
+      <c r="B54" s="12">
         <v>0.426228534997241</v>
       </c>
-      <c r="C54" s="16">
+      <c r="C54" s="12">
         <v>1.39919870453274</v>
       </c>
-      <c r="D54" s="16">
+      <c r="D54" s="12">
         <v>0.429297482953404</v>
       </c>
-      <c r="E54" s="16">
+      <c r="E54" s="12">
         <v>0.626746164553194</v>
       </c>
     </row>
     <row r="55" spans="2:5">
-      <c r="B55" s="16">
+      <c r="B55" s="12">
         <v>0.209022359030866</v>
       </c>
-      <c r="C55" s="16">
+      <c r="C55" s="12">
         <v>0.142382794327218</v>
       </c>
-      <c r="D55" s="16">
+      <c r="D55" s="12">
         <v>1.39759529830791</v>
       </c>
-      <c r="E55" s="16">
+      <c r="E55" s="12">
         <v>0.374504695979377</v>
       </c>
     </row>
     <row r="56" spans="2:5">
-      <c r="B56" s="16">
+      <c r="B56" s="12">
         <v>0.271201525892062</v>
       </c>
-      <c r="C56" s="16">
+      <c r="C56" s="12">
         <v>0.268597131734725</v>
       </c>
-      <c r="D56" s="16">
+      <c r="D56" s="12">
         <v>0.338006551517438</v>
       </c>
-      <c r="E56" s="16">
+      <c r="E56" s="12">
         <v>1.28054337638184</v>
       </c>
     </row>
     <row r="58" spans="4:7">
-      <c r="D58" s="25"/>
-      <c r="E58" s="25"/>
-      <c r="F58" s="26"/>
-      <c r="G58" s="25"/>
+      <c r="D58" s="19"/>
+      <c r="E58" s="19"/>
+      <c r="F58" s="20"/>
+      <c r="G58" s="19"/>
     </row>
     <row r="59" spans="4:7">
-      <c r="D59" s="25"/>
-      <c r="E59" s="1"/>
-      <c r="F59" s="26"/>
-      <c r="G59" s="25"/>
+      <c r="D59" s="19"/>
+      <c r="F59" s="20"/>
+      <c r="G59" s="19"/>
     </row>
     <row r="60" ht="15" spans="4:7">
-      <c r="D60" s="25"/>
-      <c r="E60" s="25"/>
-      <c r="F60" s="27"/>
-      <c r="G60" s="25"/>
+      <c r="D60" s="19"/>
+      <c r="E60" s="19"/>
+      <c r="F60" s="21"/>
+      <c r="G60" s="19"/>
     </row>
     <row r="61" spans="4:7">
-      <c r="D61" s="25"/>
-      <c r="E61" s="25"/>
-      <c r="F61" s="26"/>
-      <c r="G61" s="25"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="20"/>
+      <c r="G61" s="19"/>
     </row>
     <row r="65" spans="2:3">
       <c r="B65"/>
@@ -2970,81 +2881,81 @@
       <c r="B77" s="2"/>
     </row>
     <row r="78" spans="2:4">
-      <c r="B78" s="21" t="s">
+      <c r="B78" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C78" s="21" t="s">
+      <c r="C78" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D78" s="21" t="s">
+      <c r="D78" s="16" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="79" ht="42.75" spans="2:5">
-      <c r="B79" s="16">
+      <c r="B79" s="12">
         <f>H5/G5</f>
         <v>2.13674915816849</v>
       </c>
-      <c r="C79" s="16">
+      <c r="C79" s="12">
         <f>H140/D40</f>
         <v>2.20248386239781</v>
       </c>
-      <c r="D79" s="16">
+      <c r="D79" s="12">
         <f>C79/B79</f>
         <v>1.03076388446347</v>
       </c>
-      <c r="E79" s="28" t="s">
+      <c r="E79" s="22" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="80" ht="57" spans="2:5">
-      <c r="B80" s="16">
+      <c r="B80" s="12">
         <f>H6/G6</f>
         <v>2.68920479198688</v>
       </c>
-      <c r="C80" s="16">
+      <c r="C80" s="12">
         <f>H141/D41</f>
         <v>2.6537019758726</v>
       </c>
-      <c r="D80" s="16">
+      <c r="D80" s="12">
         <f t="shared" ref="D80:D82" si="0">C80/B80</f>
-        <v>0.986798024375061</v>
-      </c>
-      <c r="E80" s="28" t="s">
+        <v>0.986798024375062</v>
+      </c>
+      <c r="E80" s="22" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="81" ht="57" spans="2:5">
-      <c r="B81" s="16">
+      <c r="B81" s="12">
         <f>H7/G7</f>
         <v>2.1659290852527</v>
       </c>
-      <c r="C81" s="16">
+      <c r="C81" s="12">
         <f>H142/D42</f>
         <v>2.1701203772396</v>
       </c>
-      <c r="D81" s="16">
+      <c r="D81" s="12">
         <f t="shared" si="0"/>
-        <v>1.00193510120688</v>
-      </c>
-      <c r="E81" s="28" t="s">
+        <v>1.00193510120689</v>
+      </c>
+      <c r="E81" s="22" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="82" ht="42.75" spans="2:5">
-      <c r="B82" s="16">
+      <c r="B82" s="12">
         <f>H8/G8</f>
         <v>2.33024802697878</v>
       </c>
-      <c r="C82" s="16">
+      <c r="C82" s="12">
         <f>H143/D43</f>
-        <v>2.40103309929086</v>
-      </c>
-      <c r="D82" s="16">
-        <f>C82/B82</f>
+        <v>2.40103309929087</v>
+      </c>
+      <c r="D82" s="12">
+        <f t="shared" si="0"/>
         <v>1.03037662578943</v>
       </c>
-      <c r="E82" s="28" t="s">
+      <c r="E82" s="22" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3058,65 +2969,65 @@
       </c>
     </row>
     <row r="91" spans="2:9">
-      <c r="B91" s="21" t="s">
+      <c r="B91" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C91" s="21" t="s">
+      <c r="C91" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D91" s="21" t="s">
+      <c r="D91" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E91" s="21" t="s">
+      <c r="E91" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F91" s="21" t="s">
+      <c r="F91" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="H91" s="17">
+      <c r="H91" s="12">
         <f>C92</f>
         <v>0.17013295685443</v>
       </c>
-      <c r="I91" s="17">
+      <c r="I91" s="12">
         <f>C101</f>
         <v>0.169982238631332</v>
       </c>
     </row>
     <row r="92" spans="2:9">
-      <c r="B92" s="21" t="s">
+      <c r="B92" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C92" s="16">
+      <c r="C92" s="12">
         <f>C9/C12</f>
         <v>0.17013295685443</v>
       </c>
-      <c r="D92" s="16">
+      <c r="D92" s="12">
         <f>D9/D12</f>
         <v>0.201030027073591</v>
       </c>
-      <c r="E92" s="16">
+      <c r="E92" s="12">
         <f>E9/E12</f>
         <v>0.210769647587702</v>
       </c>
-      <c r="F92" s="16">
+      <c r="F92" s="12">
         <f>F9/F12</f>
         <v>0.192603771323559</v>
       </c>
-      <c r="H92" s="17">
+      <c r="H92" s="12">
         <f>D92</f>
         <v>0.201030027073591</v>
       </c>
-      <c r="I92" s="17">
+      <c r="I92" s="12">
         <f>D101</f>
         <v>0.202350970022253</v>
       </c>
     </row>
     <row r="93" spans="8:9">
-      <c r="H93" s="17">
+      <c r="H93" s="12">
         <f>E92</f>
         <v>0.210769647587702</v>
       </c>
-      <c r="I93" s="17">
+      <c r="I93" s="12">
         <f>E101</f>
         <v>0.211383752262649</v>
       </c>
@@ -3125,49 +3036,49 @@
       <c r="B94" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H94" s="17">
+      <c r="H94" s="12">
         <f>F92</f>
         <v>0.192603771323559</v>
       </c>
-      <c r="I94" s="17">
+      <c r="I94" s="12">
         <f>F101</f>
         <v>0.192505470977426</v>
       </c>
     </row>
     <row r="95" spans="2:6">
-      <c r="B95" s="21" t="s">
+      <c r="B95" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C95" s="21" t="s">
+      <c r="C95" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D95" s="21" t="s">
+      <c r="D95" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E95" s="21" t="s">
+      <c r="E95" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F95" s="21" t="s">
+      <c r="F95" s="16" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="96" spans="2:6">
-      <c r="B96" s="21" t="s">
+      <c r="B96" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C96" s="21">
+      <c r="C96" s="16">
         <f>C9*1.035</f>
         <v>1036.472805</v>
       </c>
-      <c r="D96" s="21">
+      <c r="D96" s="16">
         <f>D9*1.035</f>
         <v>1521.670455</v>
       </c>
-      <c r="E96" s="21">
+      <c r="E96" s="16">
         <f>E9*1.035</f>
         <v>1086.980805</v>
       </c>
-      <c r="F96" s="21">
+      <c r="F96" s="16">
         <f>F9*1.035</f>
         <v>997.960455</v>
       </c>
@@ -3178,45 +3089,45 @@
       </c>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="21" t="s">
+      <c r="B100" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C100" s="21" t="s">
+      <c r="C100" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D100" s="21" t="s">
+      <c r="D100" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E100" s="21" t="s">
+      <c r="E100" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F100" s="21" t="s">
+      <c r="F100" s="16" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="21" t="s">
+      <c r="B101" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C101" s="16">
+      <c r="C101" s="12">
         <f>C96/H140</f>
         <v>0.169982238631332</v>
       </c>
-      <c r="D101" s="16">
+      <c r="D101" s="12">
         <f>D96/H141</f>
         <v>0.202350970022253</v>
       </c>
-      <c r="E101" s="16">
+      <c r="E101" s="12">
         <f>E96/H142</f>
         <v>0.211383752262649</v>
       </c>
-      <c r="F101" s="16">
+      <c r="F101" s="12">
         <f>F96/H143</f>
         <v>0.192505470977426</v>
       </c>
     </row>
     <row r="102" spans="3:9">
-      <c r="C102" s="29" t="s">
+      <c r="C102" s="23" t="s">
         <v>30</v>
       </c>
       <c r="G102" t="s">
@@ -3230,222 +3141,221 @@
       <c r="C103" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G103" s="21" cm="1">
+      <c r="G103" s="16" cm="1">
         <f t="array" ref="G103:G106">MMULT(_xlfn.ANCHORARRAY(B53),H91:H94)</f>
         <v>0.415227795931282</v>
       </c>
-      <c r="H103" s="45" t="s">
+      <c r="H103" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="I103" s="21" cm="1">
+      <c r="I103" s="16" cm="1">
         <f t="array" ref="I103:L103">MMULT(C92:F92,B53:E56)</f>
         <v>0.405961849323119</v>
       </c>
-      <c r="J103" s="21">
+      <c r="J103" s="16">
         <v>0.414072904918213</v>
       </c>
-      <c r="K103" s="21">
+      <c r="K103" s="16">
         <v>0.502982144422241</v>
       </c>
-      <c r="L103" s="21">
+      <c r="L103" s="16">
         <v>0.504827546914185</v>
       </c>
-      <c r="M103" s="26"/>
+      <c r="M103" s="20"/>
     </row>
     <row r="104" ht="15" spans="6:13">
-      <c r="F104" s="44" t="s">
+      <c r="F104" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="G104" s="21">
+      <c r="G104" s="16">
         <v>0.56499302855626</v>
       </c>
-      <c r="M104" s="25"/>
+      <c r="M104" s="19"/>
     </row>
     <row r="105" spans="3:13">
-      <c r="C105" s="31"/>
-      <c r="D105" s="31"/>
-      <c r="E105" s="31"/>
-      <c r="G105" s="21">
+      <c r="C105" s="24"/>
+      <c r="D105" s="24"/>
+      <c r="E105" s="24"/>
+      <c r="G105" s="16">
         <v>0.430886494307622</v>
       </c>
-      <c r="M105" s="25"/>
+      <c r="M105" s="19"/>
     </row>
     <row r="106" spans="3:13">
-      <c r="C106" s="26"/>
-      <c r="D106" s="26"/>
-      <c r="E106" s="26"/>
-      <c r="G106" s="21">
+      <c r="C106" s="20"/>
+      <c r="D106" s="20"/>
+      <c r="E106" s="20"/>
+      <c r="G106" s="16">
         <v>0.418015411548181</v>
       </c>
-      <c r="M106" s="25"/>
+      <c r="M106" s="19"/>
     </row>
     <row r="107" spans="3:13">
-      <c r="C107" s="26"/>
-      <c r="D107" s="26"/>
-      <c r="E107" s="26"/>
-      <c r="M107" s="25"/>
+      <c r="C107" s="20"/>
+      <c r="D107" s="20"/>
+      <c r="E107" s="20"/>
+      <c r="M107" s="19"/>
     </row>
     <row r="108" spans="3:13">
-      <c r="C108" s="26"/>
-      <c r="D108" s="26"/>
-      <c r="E108" s="26"/>
-      <c r="G108" s="21" cm="1">
+      <c r="C108" s="20"/>
+      <c r="D108" s="20"/>
+      <c r="E108" s="20"/>
+      <c r="G108" s="16" cm="1">
         <f t="array" ref="G108:G111">MMULT(_xlfn.ANCHORARRAY(B53),I91:I94)</f>
         <v>0.415600725838753</v>
       </c>
-      <c r="H108" s="45" t="s">
+      <c r="H108" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="I108" s="21" cm="1">
+      <c r="I108" s="16" cm="1">
         <f t="array" ref="I108:L108">MMULT(C101:F101,B53:E56)</f>
         <v>0.406428148499177</v>
       </c>
-      <c r="J108" s="21">
+      <c r="J108" s="16">
         <v>0.415936977648065</v>
       </c>
-      <c r="K108" s="21">
+      <c r="K108" s="16">
         <v>0.504323762619469</v>
       </c>
-      <c r="L108" s="21">
+      <c r="L108" s="16">
         <v>0.505712366913626</v>
       </c>
-      <c r="M108" s="26"/>
+      <c r="M108" s="20"/>
     </row>
     <row r="109" ht="15" spans="3:13">
-      <c r="C109" s="26"/>
-      <c r="D109" s="26"/>
-      <c r="E109" s="26"/>
-      <c r="F109" s="44" t="s">
+      <c r="C109" s="20"/>
+      <c r="D109" s="20"/>
+      <c r="E109" s="20"/>
+      <c r="F109" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="G109" s="21">
+      <c r="G109" s="16">
         <v>0.566979074037673</v>
       </c>
-      <c r="M109" s="25"/>
+      <c r="M109" s="19"/>
     </row>
     <row r="110" spans="3:13">
-      <c r="C110" s="25"/>
-      <c r="D110" s="25"/>
-      <c r="E110" s="25"/>
-      <c r="G110" s="21">
+      <c r="C110" s="19"/>
+      <c r="D110" s="19"/>
+      <c r="E110" s="19"/>
+      <c r="G110" s="16">
         <v>0.43186452624239</v>
       </c>
-      <c r="M110" s="25"/>
+      <c r="M110" s="19"/>
     </row>
     <row r="111" spans="7:13">
-      <c r="G111" s="21">
+      <c r="G111" s="16">
         <v>0.418411031569606</v>
       </c>
-      <c r="M111" s="25"/>
+      <c r="M111" s="19"/>
     </row>
     <row r="112" spans="3:13">
       <c r="C112" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H112" s="25"/>
-      <c r="I112" s="25"/>
-      <c r="J112" s="25"/>
-      <c r="K112" s="25"/>
-      <c r="L112" s="26"/>
-      <c r="M112" s="25"/>
-    </row>
-    <row r="113" spans="3:12">
+      <c r="H112" s="19"/>
+      <c r="I112" s="19"/>
+      <c r="J112" s="19"/>
+      <c r="K112" s="19"/>
+      <c r="L112" s="20"/>
+      <c r="M112" s="19"/>
+    </row>
+    <row r="113" spans="3:3">
       <c r="C113" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="L113" s="30"/>
     </row>
     <row r="115" spans="2:6">
-      <c r="B115" s="21" t="s">
+      <c r="B115" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C115" s="21" t="s">
+      <c r="C115" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D115" s="21" t="s">
+      <c r="D115" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E115" s="21" t="s">
+      <c r="E115" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F115" s="21" t="s">
+      <c r="F115" s="16" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="116" spans="2:6">
-      <c r="B116" s="21" t="s">
+      <c r="B116" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C116" s="16">
+      <c r="C116" s="12">
         <f>C92/I103</f>
         <v>0.419086072097912</v>
       </c>
-      <c r="D116" s="16">
+      <c r="D116" s="12">
         <f>D92/J103</f>
         <v>0.485494280562256</v>
       </c>
-      <c r="E116" s="16">
+      <c r="E116" s="12">
         <f>E92/K103</f>
         <v>0.419040019461935</v>
       </c>
-      <c r="F116" s="16">
+      <c r="F116" s="12">
         <f>F92/L103</f>
         <v>0.381523893656103</v>
       </c>
     </row>
     <row r="117" spans="2:6">
-      <c r="B117" s="21" t="s">
+      <c r="B117" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C117" s="16">
+      <c r="C117" s="12">
         <f>C101/I108</f>
         <v>0.418234414272308</v>
       </c>
-      <c r="D117" s="16">
+      <c r="D117" s="12">
         <f>D101/J108</f>
         <v>0.48649430297459</v>
       </c>
-      <c r="E117" s="16">
+      <c r="E117" s="12">
         <f>E101/K108</f>
         <v>0.419142955241127</v>
       </c>
-      <c r="F117" s="16">
+      <c r="F117" s="12">
         <f>F101/L108</f>
-        <v>0.380661980153445</v>
+        <v>0.380661980153444</v>
       </c>
     </row>
     <row r="118" spans="2:6">
-      <c r="B118" s="21" t="s">
+      <c r="B118" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C118" s="32">
+      <c r="C118" s="25">
         <f>C117/C116</f>
-        <v>0.997967821213095</v>
-      </c>
-      <c r="D118" s="32">
+        <v>0.997967821213096</v>
+      </c>
+      <c r="D118" s="25">
         <f>D117/D116</f>
         <v>1.00205980266374</v>
       </c>
-      <c r="E118" s="32">
+      <c r="E118" s="25">
         <f>E117/E116</f>
         <v>1.00024564665524</v>
       </c>
-      <c r="F118" s="32">
+      <c r="F118" s="25">
         <f>F117/F116</f>
-        <v>0.997740866255064</v>
+        <v>0.997740866255062</v>
       </c>
     </row>
     <row r="120" ht="86" customHeight="1" spans="3:6">
-      <c r="C120" s="46" t="s">
+      <c r="C120" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="D120" s="46" t="s">
+      <c r="D120" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="E120" s="46" t="s">
+      <c r="E120" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="F120" s="46" t="s">
+      <c r="F120" s="33" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3477,60 +3387,60 @@
     </row>
     <row r="131" ht="15" spans="1:6">
       <c r="A131" s="2"/>
-      <c r="B131" s="21" t="s">
+      <c r="B131" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C131" s="21" t="s">
+      <c r="C131" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D131" s="21" t="s">
+      <c r="D131" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E131" s="21" t="s">
+      <c r="E131" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F131" s="21" t="s">
+      <c r="F131" s="16" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="132" spans="2:6">
-      <c r="B132" s="21" t="s">
+      <c r="B132" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="C132" s="16">
+      <c r="C132" s="12">
         <f>B30+(C146/C147)+(C144/C147)*(1+0.4)</f>
-        <v>0.975721334762067</v>
-      </c>
-      <c r="D132" s="16">
+        <v>0.975721334762066</v>
+      </c>
+      <c r="D132" s="12">
         <f>C30+(D145/D147)+(D144/D147)*(1+0.3)</f>
         <v>0.880260127381413</v>
       </c>
-      <c r="E132" s="16">
+      <c r="E132" s="12">
         <f>D30+(E145/E147)+(E144/E147)*(1+0.2)</f>
-        <v>0.930402082414413</v>
-      </c>
-      <c r="F132" s="16">
+        <v>0.930402082414412</v>
+      </c>
+      <c r="F132" s="12">
         <f>E30+(F145/F147)+(F144/F147)*(1+0.4)</f>
         <v>1.04142413614315</v>
       </c>
     </row>
     <row r="136" spans="2:6">
-      <c r="B136" s="34" t="s">
+      <c r="B136" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="C136" s="35">
+      <c r="C136" s="16">
         <f>C10/C9</f>
         <v>0.472128161626006</v>
       </c>
-      <c r="D136" s="35">
+      <c r="D136" s="16">
         <f>D10/D9</f>
         <v>0.666808142765708</v>
       </c>
-      <c r="E136" s="35">
+      <c r="E136" s="16">
         <f>E10/E9</f>
         <v>0.221552946374246</v>
       </c>
-      <c r="F136" s="35">
+      <c r="F136" s="16">
         <f>F10/F9</f>
         <v>0.395711321046283</v>
       </c>
@@ -3557,187 +3467,187 @@
       <c r="H139" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J139" s="38"/>
-      <c r="K139" s="38"/>
+      <c r="J139" s="20"/>
+      <c r="K139" s="20"/>
     </row>
     <row r="140" spans="2:20">
       <c r="B140" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C140" s="36">
+      <c r="C140" s="27">
         <f>B26*$H$140</f>
-        <v>920.340365663252</v>
-      </c>
-      <c r="D140" s="36">
+        <v>920.340365663255</v>
+      </c>
+      <c r="D140" s="27">
         <f>C26*$H$140</f>
-        <v>915.906022408136</v>
-      </c>
-      <c r="E140" s="36">
+        <v>915.906022408133</v>
+      </c>
+      <c r="E140" s="27">
         <f>D26*$H$140</f>
-        <v>820.257350075465</v>
-      </c>
-      <c r="F140" s="36">
+        <v>820.257350075462</v>
+      </c>
+      <c r="F140" s="27">
         <f>E26*$H$140</f>
         <v>577.503470477202</v>
       </c>
-      <c r="G140" s="36">
+      <c r="G140" s="27">
         <f>G5*1.04</f>
         <v>2864.89632</v>
       </c>
-      <c r="H140" s="21" cm="1">
+      <c r="H140" s="16" cm="1">
         <f t="array" ref="H140:H143">MMULT(_xlfn.ANCHORARRAY(B53),G140:G143)</f>
         <v>6097.53591519622</v>
       </c>
-      <c r="J140" s="31"/>
-      <c r="K140" s="38"/>
-      <c r="S140" s="20"/>
-      <c r="T140" s="43"/>
+      <c r="J140" s="24"/>
+      <c r="K140" s="20"/>
+      <c r="S140" s="15"/>
+      <c r="T140" s="30"/>
     </row>
     <row r="141" spans="2:20">
       <c r="B141" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C141" s="36">
+      <c r="C141" s="27">
         <f>$H$141*B27</f>
-        <v>1359.34684301486</v>
-      </c>
-      <c r="D141" s="36">
+        <v>1359.34684301485</v>
+      </c>
+      <c r="D141" s="27">
         <f>$H$141*C27</f>
         <v>1286.37174354449</v>
       </c>
-      <c r="E141" s="36">
+      <c r="E141" s="27">
         <f>$H$141*D27</f>
         <v>1002.24229537782</v>
       </c>
-      <c r="F141" s="36">
+      <c r="F141" s="27">
         <f>$H$141*E27</f>
         <v>2425.51713116383</v>
       </c>
-      <c r="G141" s="36">
+      <c r="G141" s="27">
         <f>G6*1.02</f>
         <v>2773.9308</v>
       </c>
-      <c r="H141" s="21">
+      <c r="H141" s="16">
         <v>7519.95631566609</v>
       </c>
-      <c r="J141" s="31"/>
-      <c r="K141" s="38"/>
-      <c r="S141" s="20"/>
-      <c r="T141" s="43"/>
+      <c r="J141" s="24"/>
+      <c r="K141" s="20"/>
+      <c r="S141" s="15"/>
+      <c r="T141" s="30"/>
     </row>
     <row r="142" spans="2:20">
       <c r="B142" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C142" s="36">
+      <c r="C142" s="27">
         <f>$H$142*B28</f>
         <v>390.361853953888</v>
       </c>
-      <c r="D142" s="36">
+      <c r="D142" s="27">
         <f>$H$142*C28</f>
         <v>132.352248279166</v>
       </c>
-      <c r="E142" s="36">
+      <c r="E142" s="27">
         <f>$H$142*D28</f>
         <v>1080.06752334035</v>
       </c>
-      <c r="F142" s="36">
+      <c r="F142" s="27">
         <f>$H$142*E28</f>
         <v>1027.79598106563</v>
       </c>
-      <c r="G142" s="36">
+      <c r="G142" s="27">
         <f>G7*1.03</f>
         <v>2369.55311</v>
       </c>
-      <c r="H142" s="21">
+      <c r="H142" s="16">
         <v>5142.21548896247</v>
       </c>
-      <c r="J142" s="31"/>
-      <c r="K142" s="38"/>
-      <c r="S142" s="20"/>
-      <c r="T142" s="43"/>
+      <c r="J142" s="24"/>
+      <c r="K142" s="20"/>
+      <c r="S142" s="15"/>
+      <c r="T142" s="30"/>
     </row>
     <row r="143" spans="2:20">
       <c r="B143" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C143" s="36">
+      <c r="C143" s="27">
         <f>$H$143*B29</f>
-        <v>631.762849382742</v>
-      </c>
-      <c r="D143" s="36">
+        <v>631.762849382743</v>
+      </c>
+      <c r="D143" s="27">
         <f>$H$143*C29</f>
-        <v>701.227183289436</v>
-      </c>
-      <c r="E143" s="36">
+        <v>701.227183289438</v>
+      </c>
+      <c r="E143" s="27">
         <f>$H$143*D29</f>
-        <v>788.33585968118</v>
-      </c>
-      <c r="F143" s="36">
+        <v>788.335859681181</v>
+      </c>
+      <c r="F143" s="27">
         <f>$H$143*E29</f>
         <v>407.522924928246</v>
       </c>
-      <c r="G143" s="36">
+      <c r="G143" s="27">
         <f>G8*1.04</f>
         <v>2234.2892</v>
       </c>
-      <c r="H143" s="21">
+      <c r="H143" s="16">
         <v>5184.06282134716</v>
       </c>
-      <c r="J143" s="31"/>
-      <c r="K143" s="38"/>
-      <c r="S143" s="20"/>
-      <c r="T143" s="43"/>
+      <c r="J143" s="24"/>
+      <c r="K143" s="20"/>
+      <c r="S143" s="15"/>
+      <c r="T143" s="30"/>
     </row>
     <row r="144" spans="2:11">
       <c r="B144" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C144" s="7">
+      <c r="C144" s="6">
         <f>C9*1.035</f>
         <v>1036.472805</v>
       </c>
-      <c r="D144" s="7">
+      <c r="D144" s="6">
         <f>D9*1.035</f>
         <v>1521.670455</v>
       </c>
-      <c r="E144" s="7">
+      <c r="E144" s="6">
         <f>E9*1.035</f>
         <v>1086.980805</v>
       </c>
-      <c r="F144" s="7">
+      <c r="F144" s="6">
         <f>F9*1.035</f>
         <v>997.960455</v>
       </c>
-      <c r="G144" s="8"/>
-      <c r="H144" s="47" t="s">
+      <c r="G144" s="7"/>
+      <c r="H144" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="J144" s="39"/>
-      <c r="K144" s="38"/>
+      <c r="J144" s="28"/>
+      <c r="K144" s="20"/>
     </row>
     <row r="145" spans="2:8">
       <c r="B145" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C145" s="36">
+      <c r="C145" s="27">
         <f>C144*C136</f>
         <v>489.348</v>
       </c>
-      <c r="D145" s="36">
+      <c r="D145" s="27">
         <f>D144*D136</f>
         <v>1014.66225</v>
       </c>
-      <c r="E145" s="36">
+      <c r="E145" s="27">
         <f>E144*E136</f>
         <v>240.8238</v>
       </c>
-      <c r="F145" s="36">
+      <c r="F145" s="27">
         <f>F144*F136</f>
         <v>394.90425</v>
       </c>
-      <c r="G145" s="8"/>
-      <c r="H145" s="47" t="s">
+      <c r="G145" s="7"/>
+      <c r="H145" s="34" t="s">
         <v>48</v>
       </c>
     </row>
@@ -3745,24 +3655,24 @@
       <c r="B146" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C146" s="36">
+      <c r="C146" s="27">
         <f>H140-C145-C144-C143-C142-C141-C140</f>
-        <v>1269.90319818149</v>
-      </c>
-      <c r="D146" s="36">
+        <v>1269.90319818148</v>
+      </c>
+      <c r="D146" s="27">
         <f>H141-D145-D144-D143-D142-D141-D140</f>
         <v>1947.76641314486</v>
       </c>
-      <c r="E146" s="36">
+      <c r="E146" s="27">
         <f>H142-E145-E144-E143-E142-E141-E140</f>
-        <v>123.50785548766</v>
-      </c>
-      <c r="F146" s="36">
+        <v>123.507855487666</v>
+      </c>
+      <c r="F146" s="27">
         <f>H143+F145-F144-F143-F142-F141-F140</f>
-        <v>142.667108712261</v>
-      </c>
-      <c r="G146" s="8"/>
-      <c r="H146" s="47" t="s">
+        <v>142.667108712266</v>
+      </c>
+      <c r="G146" s="7"/>
+      <c r="H146" s="34" t="s">
         <v>48</v>
       </c>
     </row>
@@ -3770,730 +3680,730 @@
       <c r="B147" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C147" s="37">
+      <c r="C147" s="27">
         <f>H140</f>
         <v>6097.53591519622</v>
       </c>
-      <c r="D147" s="37">
+      <c r="D147" s="27">
         <f>H141</f>
         <v>7519.95631566609</v>
       </c>
-      <c r="E147" s="37">
+      <c r="E147" s="27">
         <f>H142</f>
         <v>5142.21548896247</v>
       </c>
-      <c r="F147" s="37">
+      <c r="F147" s="27">
         <f>H143</f>
         <v>5184.06282134716</v>
       </c>
-      <c r="G147" s="11"/>
-      <c r="H147" s="10"/>
+      <c r="G147" s="7"/>
+      <c r="H147" s="6"/>
     </row>
     <row r="148" ht="15" spans="1:1">
       <c r="A148" s="2"/>
     </row>
     <row r="157" spans="10:20">
-      <c r="J157" s="38"/>
-      <c r="K157" s="38"/>
-      <c r="L157" s="38"/>
-      <c r="M157" s="38"/>
-      <c r="N157" s="38"/>
-      <c r="O157" s="38"/>
-      <c r="P157" s="38"/>
-      <c r="Q157" s="38"/>
-      <c r="R157" s="38"/>
-      <c r="S157" s="38"/>
-      <c r="T157" s="38"/>
+      <c r="J157" s="20"/>
+      <c r="K157" s="20"/>
+      <c r="L157" s="20"/>
+      <c r="M157" s="20"/>
+      <c r="N157" s="20"/>
+      <c r="O157" s="20"/>
+      <c r="P157" s="20"/>
+      <c r="Q157" s="20"/>
+      <c r="R157" s="20"/>
+      <c r="S157" s="20"/>
+      <c r="T157" s="20"/>
     </row>
     <row r="158" spans="10:20">
-      <c r="J158" s="38"/>
-      <c r="K158" s="38"/>
-      <c r="L158" s="38"/>
-      <c r="M158" s="38"/>
-      <c r="N158" s="38"/>
-      <c r="O158" s="38"/>
-      <c r="P158" s="38"/>
-      <c r="Q158" s="38"/>
-      <c r="R158" s="38"/>
-      <c r="S158" s="38"/>
-      <c r="T158" s="38"/>
+      <c r="J158" s="20"/>
+      <c r="K158" s="20"/>
+      <c r="L158" s="20"/>
+      <c r="M158" s="20"/>
+      <c r="N158" s="20"/>
+      <c r="O158" s="20"/>
+      <c r="P158" s="20"/>
+      <c r="Q158" s="20"/>
+      <c r="R158" s="20"/>
+      <c r="S158" s="20"/>
+      <c r="T158" s="20"/>
     </row>
     <row r="159" spans="10:20">
-      <c r="J159" s="38"/>
-      <c r="K159" s="38"/>
-      <c r="L159" s="38"/>
-      <c r="M159" s="38"/>
-      <c r="N159" s="38"/>
-      <c r="O159" s="38"/>
-      <c r="P159" s="38"/>
-      <c r="Q159" s="38"/>
-      <c r="R159" s="38"/>
-      <c r="S159" s="38"/>
-      <c r="T159" s="38"/>
+      <c r="J159" s="20"/>
+      <c r="K159" s="20"/>
+      <c r="L159" s="20"/>
+      <c r="M159" s="20"/>
+      <c r="N159" s="20"/>
+      <c r="O159" s="20"/>
+      <c r="P159" s="20"/>
+      <c r="Q159" s="20"/>
+      <c r="R159" s="20"/>
+      <c r="S159" s="20"/>
+      <c r="T159" s="20"/>
     </row>
     <row r="160" spans="10:20">
-      <c r="J160" s="38"/>
-      <c r="K160" s="38"/>
-      <c r="L160" s="38"/>
-      <c r="M160" s="38"/>
-      <c r="N160" s="38"/>
-      <c r="O160" s="38"/>
-      <c r="P160" s="38"/>
-      <c r="Q160" s="38"/>
-      <c r="R160" s="38"/>
-      <c r="S160" s="38"/>
-      <c r="T160" s="38"/>
+      <c r="J160" s="20"/>
+      <c r="K160" s="20"/>
+      <c r="L160" s="20"/>
+      <c r="M160" s="20"/>
+      <c r="N160" s="20"/>
+      <c r="O160" s="20"/>
+      <c r="P160" s="20"/>
+      <c r="Q160" s="20"/>
+      <c r="R160" s="20"/>
+      <c r="S160" s="20"/>
+      <c r="T160" s="20"/>
     </row>
     <row r="161" spans="10:20">
-      <c r="J161" s="38"/>
-      <c r="K161" s="38"/>
-      <c r="L161" s="38"/>
-      <c r="M161" s="38"/>
-      <c r="N161" s="38"/>
-      <c r="O161" s="38"/>
-      <c r="P161" s="38"/>
-      <c r="Q161" s="38"/>
-      <c r="R161" s="38"/>
-      <c r="S161" s="38"/>
-      <c r="T161" s="38"/>
+      <c r="J161" s="20"/>
+      <c r="K161" s="20"/>
+      <c r="L161" s="20"/>
+      <c r="M161" s="20"/>
+      <c r="N161" s="20"/>
+      <c r="O161" s="20"/>
+      <c r="P161" s="20"/>
+      <c r="Q161" s="20"/>
+      <c r="R161" s="20"/>
+      <c r="S161" s="20"/>
+      <c r="T161" s="20"/>
     </row>
     <row r="162" spans="1:20">
-      <c r="A162" s="38"/>
-      <c r="B162" s="38"/>
-      <c r="C162" s="38"/>
-      <c r="D162" s="25"/>
-      <c r="E162" s="25"/>
-      <c r="F162" s="25"/>
-      <c r="G162" s="25"/>
-      <c r="H162" s="38"/>
-      <c r="I162" s="38"/>
-      <c r="J162" s="38"/>
-      <c r="K162" s="38"/>
-      <c r="L162" s="38"/>
-      <c r="M162" s="38"/>
-      <c r="N162" s="38"/>
-      <c r="O162" s="38"/>
-      <c r="P162" s="38"/>
-      <c r="Q162" s="38"/>
-      <c r="R162" s="38"/>
-      <c r="S162" s="38"/>
-      <c r="T162" s="38"/>
+      <c r="A162" s="20"/>
+      <c r="B162" s="20"/>
+      <c r="C162" s="20"/>
+      <c r="D162" s="19"/>
+      <c r="E162" s="19"/>
+      <c r="F162" s="19"/>
+      <c r="G162" s="19"/>
+      <c r="H162" s="20"/>
+      <c r="I162" s="20"/>
+      <c r="J162" s="20"/>
+      <c r="K162" s="20"/>
+      <c r="L162" s="20"/>
+      <c r="M162" s="20"/>
+      <c r="N162" s="20"/>
+      <c r="O162" s="20"/>
+      <c r="P162" s="20"/>
+      <c r="Q162" s="20"/>
+      <c r="R162" s="20"/>
+      <c r="S162" s="20"/>
+      <c r="T162" s="20"/>
     </row>
     <row r="163" spans="1:20">
-      <c r="A163" s="38"/>
-      <c r="B163" s="39"/>
-      <c r="C163" s="40"/>
-      <c r="D163" s="25"/>
-      <c r="E163" s="25"/>
-      <c r="F163" s="25"/>
-      <c r="G163" s="25"/>
-      <c r="H163" s="38"/>
-      <c r="I163" s="38"/>
-      <c r="J163" s="38"/>
-      <c r="K163" s="38"/>
-      <c r="L163" s="38"/>
-      <c r="M163" s="38"/>
-      <c r="N163" s="38"/>
-      <c r="O163" s="38"/>
-      <c r="P163" s="38"/>
-      <c r="Q163" s="38"/>
-      <c r="R163" s="38"/>
-      <c r="S163" s="38"/>
-      <c r="T163" s="38"/>
+      <c r="A163" s="20"/>
+      <c r="B163" s="28"/>
+      <c r="C163" s="20"/>
+      <c r="D163" s="19"/>
+      <c r="E163" s="19"/>
+      <c r="F163" s="19"/>
+      <c r="G163" s="19"/>
+      <c r="H163" s="20"/>
+      <c r="I163" s="20"/>
+      <c r="J163" s="20"/>
+      <c r="K163" s="20"/>
+      <c r="L163" s="20"/>
+      <c r="M163" s="20"/>
+      <c r="N163" s="20"/>
+      <c r="O163" s="20"/>
+      <c r="P163" s="20"/>
+      <c r="Q163" s="20"/>
+      <c r="R163" s="20"/>
+      <c r="S163" s="20"/>
+      <c r="T163" s="20"/>
     </row>
     <row r="164" spans="1:20">
-      <c r="A164" s="38"/>
-      <c r="B164" s="38"/>
-      <c r="C164" s="40"/>
-      <c r="D164" s="25"/>
-      <c r="E164" s="25"/>
-      <c r="F164" s="25"/>
-      <c r="G164" s="25"/>
-      <c r="H164" s="38"/>
-      <c r="I164" s="38"/>
-      <c r="J164" s="38"/>
-      <c r="K164" s="38"/>
-      <c r="L164" s="38"/>
-      <c r="M164" s="38"/>
-      <c r="N164" s="38"/>
-      <c r="O164" s="38"/>
-      <c r="P164" s="38"/>
-      <c r="Q164" s="38"/>
-      <c r="R164" s="38"/>
-      <c r="S164" s="38"/>
-      <c r="T164" s="38"/>
+      <c r="A164" s="20"/>
+      <c r="B164" s="20"/>
+      <c r="C164" s="20"/>
+      <c r="D164" s="19"/>
+      <c r="E164" s="19"/>
+      <c r="F164" s="19"/>
+      <c r="G164" s="19"/>
+      <c r="H164" s="20"/>
+      <c r="I164" s="20"/>
+      <c r="J164" s="20"/>
+      <c r="K164" s="20"/>
+      <c r="L164" s="20"/>
+      <c r="M164" s="20"/>
+      <c r="N164" s="20"/>
+      <c r="O164" s="20"/>
+      <c r="P164" s="20"/>
+      <c r="Q164" s="20"/>
+      <c r="R164" s="20"/>
+      <c r="S164" s="20"/>
+      <c r="T164" s="20"/>
     </row>
     <row r="165" spans="1:20">
-      <c r="A165" s="38"/>
-      <c r="B165" s="38"/>
-      <c r="C165" s="40"/>
-      <c r="D165" s="25"/>
-      <c r="E165" s="25"/>
-      <c r="F165" s="25"/>
-      <c r="G165" s="25"/>
-      <c r="H165" s="38"/>
-      <c r="I165" s="38"/>
-      <c r="J165" s="38"/>
-      <c r="K165" s="38"/>
-      <c r="L165" s="38"/>
-      <c r="M165" s="38"/>
-      <c r="N165" s="38"/>
-      <c r="O165" s="38"/>
-      <c r="P165" s="38"/>
-      <c r="Q165" s="38"/>
-      <c r="R165" s="38"/>
-      <c r="S165" s="38"/>
-      <c r="T165" s="38"/>
+      <c r="A165" s="20"/>
+      <c r="B165" s="20"/>
+      <c r="C165" s="20"/>
+      <c r="D165" s="19"/>
+      <c r="E165" s="19"/>
+      <c r="F165" s="19"/>
+      <c r="G165" s="19"/>
+      <c r="H165" s="20"/>
+      <c r="I165" s="20"/>
+      <c r="J165" s="20"/>
+      <c r="K165" s="20"/>
+      <c r="L165" s="20"/>
+      <c r="M165" s="20"/>
+      <c r="N165" s="20"/>
+      <c r="O165" s="20"/>
+      <c r="P165" s="20"/>
+      <c r="Q165" s="20"/>
+      <c r="R165" s="20"/>
+      <c r="S165" s="20"/>
+      <c r="T165" s="20"/>
     </row>
     <row r="166" spans="1:20">
-      <c r="A166" s="38"/>
-      <c r="B166" s="38"/>
-      <c r="C166" s="40"/>
-      <c r="D166" s="38"/>
-      <c r="E166" s="38"/>
-      <c r="F166" s="38"/>
-      <c r="G166" s="38"/>
-      <c r="H166" s="38"/>
-      <c r="I166" s="38"/>
-      <c r="J166" s="38"/>
-      <c r="K166" s="38"/>
-      <c r="L166" s="38"/>
-      <c r="M166" s="38"/>
-      <c r="N166" s="38"/>
-      <c r="O166" s="38"/>
-      <c r="P166" s="38"/>
-      <c r="Q166" s="38"/>
-      <c r="R166" s="38"/>
-      <c r="S166" s="38"/>
-      <c r="T166" s="38"/>
+      <c r="A166" s="20"/>
+      <c r="B166" s="20"/>
+      <c r="C166" s="20"/>
+      <c r="D166" s="20"/>
+      <c r="E166" s="20"/>
+      <c r="F166" s="20"/>
+      <c r="G166" s="20"/>
+      <c r="H166" s="20"/>
+      <c r="I166" s="20"/>
+      <c r="J166" s="20"/>
+      <c r="K166" s="20"/>
+      <c r="L166" s="20"/>
+      <c r="M166" s="20"/>
+      <c r="N166" s="20"/>
+      <c r="O166" s="20"/>
+      <c r="P166" s="20"/>
+      <c r="Q166" s="20"/>
+      <c r="R166" s="20"/>
+      <c r="S166" s="20"/>
+      <c r="T166" s="20"/>
     </row>
     <row r="167" spans="1:20">
-      <c r="A167" s="38"/>
-      <c r="B167" s="38"/>
-      <c r="C167" s="40"/>
-      <c r="D167" s="38"/>
-      <c r="E167" s="38"/>
-      <c r="F167" s="38"/>
-      <c r="G167" s="38"/>
-      <c r="H167" s="38"/>
-      <c r="I167" s="38"/>
-      <c r="J167" s="38"/>
-      <c r="K167" s="38"/>
-      <c r="L167" s="38"/>
-      <c r="M167" s="38"/>
-      <c r="N167" s="38"/>
-      <c r="O167" s="38"/>
-      <c r="P167" s="38"/>
-      <c r="Q167" s="38"/>
-      <c r="R167" s="38"/>
-      <c r="S167" s="38"/>
-      <c r="T167" s="38"/>
+      <c r="A167" s="20"/>
+      <c r="B167" s="20"/>
+      <c r="C167" s="20"/>
+      <c r="D167" s="20"/>
+      <c r="E167" s="20"/>
+      <c r="F167" s="20"/>
+      <c r="G167" s="20"/>
+      <c r="H167" s="20"/>
+      <c r="I167" s="20"/>
+      <c r="J167" s="20"/>
+      <c r="K167" s="20"/>
+      <c r="L167" s="20"/>
+      <c r="M167" s="20"/>
+      <c r="N167" s="20"/>
+      <c r="O167" s="20"/>
+      <c r="P167" s="20"/>
+      <c r="Q167" s="20"/>
+      <c r="R167" s="20"/>
+      <c r="S167" s="20"/>
+      <c r="T167" s="20"/>
     </row>
     <row r="168" spans="1:20">
-      <c r="A168" s="38"/>
-      <c r="B168" s="38"/>
-      <c r="C168" s="40"/>
-      <c r="D168" s="38"/>
-      <c r="E168" s="38"/>
-      <c r="F168" s="38"/>
-      <c r="G168" s="38"/>
-      <c r="H168" s="38"/>
-      <c r="I168" s="38"/>
-      <c r="J168" s="38"/>
-      <c r="K168" s="38"/>
-      <c r="L168" s="38"/>
-      <c r="M168" s="38"/>
-      <c r="N168" s="38"/>
-      <c r="O168" s="38"/>
-      <c r="P168" s="38"/>
-      <c r="Q168" s="38"/>
-      <c r="R168" s="38"/>
-      <c r="S168" s="38"/>
-      <c r="T168" s="38"/>
+      <c r="A168" s="20"/>
+      <c r="B168" s="20"/>
+      <c r="C168" s="20"/>
+      <c r="D168" s="20"/>
+      <c r="E168" s="20"/>
+      <c r="F168" s="20"/>
+      <c r="G168" s="20"/>
+      <c r="H168" s="20"/>
+      <c r="I168" s="20"/>
+      <c r="J168" s="20"/>
+      <c r="K168" s="20"/>
+      <c r="L168" s="20"/>
+      <c r="M168" s="20"/>
+      <c r="N168" s="20"/>
+      <c r="O168" s="20"/>
+      <c r="P168" s="20"/>
+      <c r="Q168" s="20"/>
+      <c r="R168" s="20"/>
+      <c r="S168" s="20"/>
+      <c r="T168" s="20"/>
     </row>
     <row r="169" spans="1:20">
-      <c r="A169" s="38"/>
-      <c r="B169" s="38"/>
-      <c r="C169" s="40"/>
-      <c r="D169" s="38"/>
-      <c r="E169" s="38"/>
-      <c r="F169" s="38"/>
-      <c r="G169" s="38"/>
-      <c r="H169" s="38"/>
-      <c r="I169" s="25"/>
-      <c r="J169" s="25"/>
-      <c r="K169" s="25"/>
-      <c r="L169" s="25"/>
-      <c r="M169" s="38"/>
-      <c r="N169" s="25"/>
-      <c r="O169" s="25"/>
-      <c r="P169" s="25"/>
-      <c r="Q169" s="25"/>
-      <c r="R169" s="38"/>
-      <c r="S169" s="38"/>
-      <c r="T169" s="38"/>
+      <c r="A169" s="20"/>
+      <c r="B169" s="20"/>
+      <c r="C169" s="20"/>
+      <c r="D169" s="20"/>
+      <c r="E169" s="20"/>
+      <c r="F169" s="20"/>
+      <c r="G169" s="20"/>
+      <c r="H169" s="20"/>
+      <c r="I169" s="19"/>
+      <c r="J169" s="19"/>
+      <c r="K169" s="19"/>
+      <c r="L169" s="19"/>
+      <c r="M169" s="20"/>
+      <c r="N169" s="19"/>
+      <c r="O169" s="19"/>
+      <c r="P169" s="19"/>
+      <c r="Q169" s="19"/>
+      <c r="R169" s="20"/>
+      <c r="S169" s="20"/>
+      <c r="T169" s="20"/>
     </row>
     <row r="170" spans="1:20">
-      <c r="A170" s="38"/>
-      <c r="B170" s="38"/>
-      <c r="C170" s="40"/>
-      <c r="D170" s="38"/>
-      <c r="E170" s="38"/>
-      <c r="F170" s="38"/>
-      <c r="G170" s="38"/>
-      <c r="H170" s="40"/>
-      <c r="I170" s="25"/>
-      <c r="J170" s="25"/>
-      <c r="K170" s="25"/>
-      <c r="L170" s="25"/>
-      <c r="M170" s="40"/>
-      <c r="N170" s="25"/>
-      <c r="O170" s="25"/>
-      <c r="P170" s="25"/>
-      <c r="Q170" s="25"/>
-      <c r="R170" s="38"/>
-      <c r="S170" s="38"/>
-      <c r="T170" s="38"/>
+      <c r="A170" s="20"/>
+      <c r="B170" s="20"/>
+      <c r="C170" s="20"/>
+      <c r="D170" s="20"/>
+      <c r="E170" s="20"/>
+      <c r="F170" s="20"/>
+      <c r="G170" s="20"/>
+      <c r="H170" s="20"/>
+      <c r="I170" s="19"/>
+      <c r="J170" s="19"/>
+      <c r="K170" s="19"/>
+      <c r="L170" s="19"/>
+      <c r="M170" s="20"/>
+      <c r="N170" s="19"/>
+      <c r="O170" s="19"/>
+      <c r="P170" s="19"/>
+      <c r="Q170" s="19"/>
+      <c r="R170" s="20"/>
+      <c r="S170" s="20"/>
+      <c r="T170" s="20"/>
     </row>
     <row r="171" spans="1:20">
-      <c r="A171" s="38"/>
-      <c r="B171" s="39"/>
-      <c r="C171" s="40"/>
-      <c r="D171" s="38"/>
-      <c r="E171" s="38"/>
-      <c r="F171" s="38"/>
-      <c r="G171" s="38"/>
-      <c r="H171" s="38"/>
-      <c r="I171" s="25"/>
-      <c r="J171" s="25"/>
-      <c r="K171" s="25"/>
-      <c r="L171" s="25"/>
-      <c r="M171" s="38"/>
-      <c r="N171" s="25"/>
-      <c r="O171" s="25"/>
-      <c r="P171" s="25"/>
-      <c r="Q171" s="25"/>
-      <c r="R171" s="38"/>
-      <c r="S171" s="38"/>
-      <c r="T171" s="38"/>
+      <c r="A171" s="20"/>
+      <c r="B171" s="28"/>
+      <c r="C171" s="20"/>
+      <c r="D171" s="20"/>
+      <c r="E171" s="20"/>
+      <c r="F171" s="20"/>
+      <c r="G171" s="20"/>
+      <c r="H171" s="20"/>
+      <c r="I171" s="19"/>
+      <c r="J171" s="19"/>
+      <c r="K171" s="19"/>
+      <c r="L171" s="19"/>
+      <c r="M171" s="20"/>
+      <c r="N171" s="19"/>
+      <c r="O171" s="19"/>
+      <c r="P171" s="19"/>
+      <c r="Q171" s="19"/>
+      <c r="R171" s="20"/>
+      <c r="S171" s="20"/>
+      <c r="T171" s="20"/>
     </row>
     <row r="172" spans="1:20">
-      <c r="A172" s="38"/>
-      <c r="B172" s="38"/>
-      <c r="C172" s="40"/>
-      <c r="D172" s="38"/>
-      <c r="E172" s="38"/>
-      <c r="F172" s="38"/>
-      <c r="G172" s="38"/>
-      <c r="H172" s="38"/>
-      <c r="I172" s="25"/>
-      <c r="J172" s="25"/>
-      <c r="K172" s="25"/>
-      <c r="L172" s="25"/>
-      <c r="M172" s="38"/>
-      <c r="N172" s="25"/>
-      <c r="O172" s="25"/>
-      <c r="P172" s="25"/>
-      <c r="Q172" s="25"/>
-      <c r="R172" s="38"/>
-      <c r="S172" s="38"/>
-      <c r="T172" s="38"/>
+      <c r="A172" s="20"/>
+      <c r="B172" s="20"/>
+      <c r="C172" s="20"/>
+      <c r="D172" s="20"/>
+      <c r="E172" s="20"/>
+      <c r="F172" s="20"/>
+      <c r="G172" s="20"/>
+      <c r="H172" s="20"/>
+      <c r="I172" s="19"/>
+      <c r="J172" s="19"/>
+      <c r="K172" s="19"/>
+      <c r="L172" s="19"/>
+      <c r="M172" s="20"/>
+      <c r="N172" s="19"/>
+      <c r="O172" s="19"/>
+      <c r="P172" s="19"/>
+      <c r="Q172" s="19"/>
+      <c r="R172" s="20"/>
+      <c r="S172" s="20"/>
+      <c r="T172" s="20"/>
     </row>
     <row r="173" spans="1:20">
-      <c r="A173" s="38"/>
-      <c r="B173" s="38"/>
-      <c r="C173" s="40"/>
-      <c r="D173" s="38"/>
-      <c r="E173" s="38"/>
-      <c r="F173" s="38"/>
-      <c r="G173" s="38"/>
-      <c r="H173" s="38"/>
-      <c r="I173" s="38"/>
-      <c r="J173" s="38"/>
-      <c r="K173" s="38"/>
-      <c r="L173" s="38"/>
-      <c r="M173" s="38"/>
-      <c r="N173" s="38"/>
-      <c r="O173" s="38"/>
-      <c r="P173" s="38"/>
-      <c r="Q173" s="38"/>
-      <c r="R173" s="38"/>
-      <c r="S173" s="38"/>
-      <c r="T173" s="38"/>
+      <c r="A173" s="20"/>
+      <c r="B173" s="20"/>
+      <c r="C173" s="20"/>
+      <c r="D173" s="20"/>
+      <c r="E173" s="20"/>
+      <c r="F173" s="20"/>
+      <c r="G173" s="20"/>
+      <c r="H173" s="20"/>
+      <c r="I173" s="20"/>
+      <c r="J173" s="20"/>
+      <c r="K173" s="20"/>
+      <c r="L173" s="20"/>
+      <c r="M173" s="20"/>
+      <c r="N173" s="20"/>
+      <c r="O173" s="20"/>
+      <c r="P173" s="20"/>
+      <c r="Q173" s="20"/>
+      <c r="R173" s="20"/>
+      <c r="S173" s="20"/>
+      <c r="T173" s="20"/>
     </row>
     <row r="174" spans="1:20">
-      <c r="A174" s="38"/>
-      <c r="B174" s="38"/>
-      <c r="C174" s="40"/>
-      <c r="D174" s="38"/>
-      <c r="E174" s="38"/>
-      <c r="F174" s="38"/>
-      <c r="G174" s="38"/>
-      <c r="H174" s="38"/>
-      <c r="I174" s="38"/>
-      <c r="J174" s="38"/>
-      <c r="K174" s="38"/>
-      <c r="L174" s="38"/>
-      <c r="M174" s="38"/>
-      <c r="N174" s="38"/>
-      <c r="O174" s="38"/>
-      <c r="P174" s="38"/>
-      <c r="Q174" s="38"/>
-      <c r="R174" s="38"/>
-      <c r="S174" s="38"/>
-      <c r="T174" s="38"/>
+      <c r="A174" s="20"/>
+      <c r="B174" s="20"/>
+      <c r="C174" s="20"/>
+      <c r="D174" s="20"/>
+      <c r="E174" s="20"/>
+      <c r="F174" s="20"/>
+      <c r="G174" s="20"/>
+      <c r="H174" s="20"/>
+      <c r="I174" s="20"/>
+      <c r="J174" s="20"/>
+      <c r="K174" s="20"/>
+      <c r="L174" s="20"/>
+      <c r="M174" s="20"/>
+      <c r="N174" s="20"/>
+      <c r="O174" s="20"/>
+      <c r="P174" s="20"/>
+      <c r="Q174" s="20"/>
+      <c r="R174" s="20"/>
+      <c r="S174" s="20"/>
+      <c r="T174" s="20"/>
     </row>
     <row r="175" spans="1:20">
-      <c r="A175" s="38"/>
-      <c r="B175" s="38"/>
-      <c r="C175" s="40"/>
-      <c r="D175" s="38"/>
-      <c r="E175" s="38"/>
-      <c r="F175" s="38"/>
-      <c r="G175" s="38"/>
-      <c r="H175" s="38"/>
-      <c r="I175" s="38"/>
-      <c r="J175" s="38"/>
-      <c r="K175" s="38"/>
-      <c r="L175" s="38"/>
-      <c r="M175" s="38"/>
-      <c r="N175" s="38"/>
-      <c r="O175" s="38"/>
-      <c r="P175" s="38"/>
-      <c r="Q175" s="38"/>
-      <c r="R175" s="38"/>
-      <c r="S175" s="38"/>
-      <c r="T175" s="38"/>
+      <c r="A175" s="20"/>
+      <c r="B175" s="20"/>
+      <c r="C175" s="20"/>
+      <c r="D175" s="20"/>
+      <c r="E175" s="20"/>
+      <c r="F175" s="20"/>
+      <c r="G175" s="20"/>
+      <c r="H175" s="20"/>
+      <c r="I175" s="20"/>
+      <c r="J175" s="20"/>
+      <c r="K175" s="20"/>
+      <c r="L175" s="20"/>
+      <c r="M175" s="20"/>
+      <c r="N175" s="20"/>
+      <c r="O175" s="20"/>
+      <c r="P175" s="20"/>
+      <c r="Q175" s="20"/>
+      <c r="R175" s="20"/>
+      <c r="S175" s="20"/>
+      <c r="T175" s="20"/>
     </row>
     <row r="176" spans="1:20">
-      <c r="A176" s="38"/>
-      <c r="B176" s="38"/>
-      <c r="C176" s="40"/>
-      <c r="D176" s="38"/>
-      <c r="E176" s="38"/>
-      <c r="F176" s="38"/>
-      <c r="G176" s="38"/>
-      <c r="H176" s="38"/>
-      <c r="I176" s="38"/>
-      <c r="J176" s="38"/>
-      <c r="K176" s="38"/>
-      <c r="L176" s="38"/>
-      <c r="M176" s="38"/>
-      <c r="N176" s="38"/>
-      <c r="O176" s="38"/>
-      <c r="P176" s="38"/>
-      <c r="Q176" s="38"/>
-      <c r="R176" s="38"/>
-      <c r="S176" s="38"/>
-      <c r="T176" s="38"/>
+      <c r="A176" s="20"/>
+      <c r="B176" s="20"/>
+      <c r="C176" s="20"/>
+      <c r="D176" s="20"/>
+      <c r="E176" s="20"/>
+      <c r="F176" s="20"/>
+      <c r="G176" s="20"/>
+      <c r="H176" s="20"/>
+      <c r="I176" s="20"/>
+      <c r="J176" s="20"/>
+      <c r="K176" s="20"/>
+      <c r="L176" s="20"/>
+      <c r="M176" s="20"/>
+      <c r="N176" s="20"/>
+      <c r="O176" s="20"/>
+      <c r="P176" s="20"/>
+      <c r="Q176" s="20"/>
+      <c r="R176" s="20"/>
+      <c r="S176" s="20"/>
+      <c r="T176" s="20"/>
     </row>
     <row r="177" spans="1:20">
-      <c r="A177" s="38"/>
-      <c r="B177" s="38"/>
-      <c r="C177" s="41"/>
-      <c r="D177" s="25"/>
-      <c r="E177" s="25"/>
-      <c r="F177" s="25"/>
-      <c r="G177" s="25"/>
-      <c r="H177" s="38"/>
-      <c r="I177" s="38"/>
-      <c r="J177" s="38"/>
-      <c r="K177" s="38"/>
-      <c r="L177" s="38"/>
-      <c r="M177" s="38"/>
-      <c r="N177" s="38"/>
-      <c r="O177" s="38"/>
-      <c r="P177" s="38"/>
-      <c r="Q177" s="38"/>
-      <c r="R177" s="38"/>
-      <c r="S177" s="38"/>
-      <c r="T177" s="38"/>
+      <c r="A177" s="20"/>
+      <c r="B177" s="20"/>
+      <c r="C177" s="19"/>
+      <c r="D177" s="19"/>
+      <c r="E177" s="19"/>
+      <c r="F177" s="19"/>
+      <c r="G177" s="19"/>
+      <c r="H177" s="20"/>
+      <c r="I177" s="20"/>
+      <c r="J177" s="20"/>
+      <c r="K177" s="20"/>
+      <c r="L177" s="20"/>
+      <c r="M177" s="20"/>
+      <c r="N177" s="20"/>
+      <c r="O177" s="20"/>
+      <c r="P177" s="20"/>
+      <c r="Q177" s="20"/>
+      <c r="R177" s="20"/>
+      <c r="S177" s="20"/>
+      <c r="T177" s="20"/>
     </row>
     <row r="178" spans="1:20">
-      <c r="A178" s="38"/>
-      <c r="B178" s="38"/>
-      <c r="C178" s="41"/>
-      <c r="D178" s="25"/>
-      <c r="E178" s="25"/>
-      <c r="F178" s="25"/>
-      <c r="G178" s="25"/>
-      <c r="H178" s="38"/>
-      <c r="I178" s="38"/>
-      <c r="J178" s="38"/>
-      <c r="K178" s="38"/>
-      <c r="L178" s="38"/>
-      <c r="M178" s="38"/>
-      <c r="N178" s="38"/>
-      <c r="O178" s="38"/>
-      <c r="P178" s="38"/>
-      <c r="Q178" s="38"/>
-      <c r="R178" s="38"/>
-      <c r="S178" s="38"/>
-      <c r="T178" s="38"/>
+      <c r="A178" s="20"/>
+      <c r="B178" s="20"/>
+      <c r="C178" s="19"/>
+      <c r="D178" s="19"/>
+      <c r="E178" s="19"/>
+      <c r="F178" s="19"/>
+      <c r="G178" s="19"/>
+      <c r="H178" s="20"/>
+      <c r="I178" s="20"/>
+      <c r="J178" s="20"/>
+      <c r="K178" s="20"/>
+      <c r="L178" s="20"/>
+      <c r="M178" s="20"/>
+      <c r="N178" s="20"/>
+      <c r="O178" s="20"/>
+      <c r="P178" s="20"/>
+      <c r="Q178" s="20"/>
+      <c r="R178" s="20"/>
+      <c r="S178" s="20"/>
+      <c r="T178" s="20"/>
     </row>
     <row r="179" spans="1:20">
-      <c r="A179" s="38"/>
-      <c r="B179" s="38"/>
-      <c r="C179" s="40"/>
-      <c r="D179" s="25"/>
-      <c r="E179" s="25"/>
-      <c r="F179" s="25"/>
-      <c r="G179" s="25"/>
-      <c r="H179" s="38"/>
-      <c r="I179" s="38"/>
-      <c r="J179" s="38"/>
-      <c r="K179" s="38"/>
-      <c r="L179" s="38"/>
-      <c r="M179" s="38"/>
-      <c r="N179" s="38"/>
-      <c r="O179" s="38"/>
-      <c r="P179" s="38"/>
-      <c r="Q179" s="38"/>
-      <c r="R179" s="38"/>
-      <c r="S179" s="38"/>
-      <c r="T179" s="38"/>
+      <c r="A179" s="20"/>
+      <c r="B179" s="20"/>
+      <c r="C179" s="20"/>
+      <c r="D179" s="19"/>
+      <c r="E179" s="19"/>
+      <c r="F179" s="19"/>
+      <c r="G179" s="19"/>
+      <c r="H179" s="20"/>
+      <c r="I179" s="20"/>
+      <c r="J179" s="20"/>
+      <c r="K179" s="20"/>
+      <c r="L179" s="20"/>
+      <c r="M179" s="20"/>
+      <c r="N179" s="20"/>
+      <c r="O179" s="20"/>
+      <c r="P179" s="20"/>
+      <c r="Q179" s="20"/>
+      <c r="R179" s="20"/>
+      <c r="S179" s="20"/>
+      <c r="T179" s="20"/>
     </row>
     <row r="180" spans="1:20">
-      <c r="A180" s="38"/>
-      <c r="B180" s="38"/>
-      <c r="C180" s="25"/>
-      <c r="D180" s="25"/>
-      <c r="E180" s="25"/>
-      <c r="F180" s="25"/>
-      <c r="G180" s="25"/>
-      <c r="H180" s="38"/>
-      <c r="I180" s="38"/>
-      <c r="J180" s="38"/>
-      <c r="K180" s="38"/>
-      <c r="L180" s="38"/>
-      <c r="M180" s="38"/>
-      <c r="N180" s="38"/>
-      <c r="O180" s="38"/>
-      <c r="P180" s="38"/>
-      <c r="Q180" s="38"/>
-      <c r="R180" s="38"/>
-      <c r="S180" s="38"/>
-      <c r="T180" s="38"/>
+      <c r="A180" s="20"/>
+      <c r="B180" s="20"/>
+      <c r="C180" s="19"/>
+      <c r="D180" s="19"/>
+      <c r="E180" s="19"/>
+      <c r="F180" s="19"/>
+      <c r="G180" s="19"/>
+      <c r="H180" s="20"/>
+      <c r="I180" s="20"/>
+      <c r="J180" s="20"/>
+      <c r="K180" s="20"/>
+      <c r="L180" s="20"/>
+      <c r="M180" s="20"/>
+      <c r="N180" s="20"/>
+      <c r="O180" s="20"/>
+      <c r="P180" s="20"/>
+      <c r="Q180" s="20"/>
+      <c r="R180" s="20"/>
+      <c r="S180" s="20"/>
+      <c r="T180" s="20"/>
     </row>
     <row r="181" spans="1:20">
-      <c r="A181" s="38"/>
-      <c r="B181" s="38"/>
-      <c r="C181" s="38"/>
-      <c r="D181" s="38"/>
-      <c r="E181" s="38"/>
-      <c r="F181" s="38"/>
-      <c r="G181" s="38"/>
-      <c r="H181" s="38"/>
-      <c r="I181" s="38"/>
-      <c r="J181" s="38"/>
-      <c r="K181" s="38"/>
-      <c r="L181" s="38"/>
-      <c r="M181" s="38"/>
-      <c r="N181" s="38"/>
-      <c r="O181" s="38"/>
-      <c r="P181" s="38"/>
-      <c r="Q181" s="38"/>
-      <c r="R181" s="38"/>
-      <c r="S181" s="38"/>
-      <c r="T181" s="38"/>
+      <c r="A181" s="20"/>
+      <c r="B181" s="20"/>
+      <c r="C181" s="20"/>
+      <c r="D181" s="20"/>
+      <c r="E181" s="20"/>
+      <c r="F181" s="20"/>
+      <c r="G181" s="20"/>
+      <c r="H181" s="20"/>
+      <c r="I181" s="20"/>
+      <c r="J181" s="20"/>
+      <c r="K181" s="20"/>
+      <c r="L181" s="20"/>
+      <c r="M181" s="20"/>
+      <c r="N181" s="20"/>
+      <c r="O181" s="20"/>
+      <c r="P181" s="20"/>
+      <c r="Q181" s="20"/>
+      <c r="R181" s="20"/>
+      <c r="S181" s="20"/>
+      <c r="T181" s="20"/>
     </row>
     <row r="182" spans="1:20">
-      <c r="A182" s="38"/>
-      <c r="B182" s="38"/>
-      <c r="C182" s="38"/>
-      <c r="D182" s="38"/>
-      <c r="E182" s="38"/>
-      <c r="F182" s="38"/>
-      <c r="G182" s="38"/>
-      <c r="H182" s="38"/>
-      <c r="I182" s="38"/>
-      <c r="J182" s="38"/>
-      <c r="K182" s="38"/>
-      <c r="L182" s="38"/>
-      <c r="M182" s="38"/>
-      <c r="N182" s="38"/>
-      <c r="O182" s="38"/>
-      <c r="P182" s="38"/>
-      <c r="Q182" s="38"/>
-      <c r="R182" s="38"/>
-      <c r="S182" s="38"/>
-      <c r="T182" s="38"/>
+      <c r="A182" s="20"/>
+      <c r="B182" s="20"/>
+      <c r="C182" s="20"/>
+      <c r="D182" s="20"/>
+      <c r="E182" s="20"/>
+      <c r="F182" s="20"/>
+      <c r="G182" s="20"/>
+      <c r="H182" s="20"/>
+      <c r="I182" s="20"/>
+      <c r="J182" s="20"/>
+      <c r="K182" s="20"/>
+      <c r="L182" s="20"/>
+      <c r="M182" s="20"/>
+      <c r="N182" s="20"/>
+      <c r="O182" s="20"/>
+      <c r="P182" s="20"/>
+      <c r="Q182" s="20"/>
+      <c r="R182" s="20"/>
+      <c r="S182" s="20"/>
+      <c r="T182" s="20"/>
     </row>
     <row r="183" spans="1:20">
-      <c r="A183" s="38"/>
-      <c r="B183" s="38"/>
-      <c r="C183" s="38"/>
-      <c r="D183" s="38"/>
-      <c r="E183" s="38"/>
-      <c r="F183" s="38"/>
-      <c r="G183" s="38"/>
-      <c r="H183" s="38"/>
-      <c r="I183" s="38"/>
-      <c r="J183" s="38"/>
-      <c r="K183" s="38"/>
-      <c r="L183" s="38"/>
-      <c r="M183" s="38"/>
-      <c r="N183" s="38"/>
-      <c r="O183" s="38"/>
-      <c r="P183" s="38"/>
-      <c r="Q183" s="38"/>
-      <c r="R183" s="38"/>
-      <c r="S183" s="38"/>
-      <c r="T183" s="38"/>
+      <c r="A183" s="20"/>
+      <c r="B183" s="20"/>
+      <c r="C183" s="20"/>
+      <c r="D183" s="20"/>
+      <c r="E183" s="20"/>
+      <c r="F183" s="20"/>
+      <c r="G183" s="20"/>
+      <c r="H183" s="20"/>
+      <c r="I183" s="20"/>
+      <c r="J183" s="20"/>
+      <c r="K183" s="20"/>
+      <c r="L183" s="20"/>
+      <c r="M183" s="20"/>
+      <c r="N183" s="20"/>
+      <c r="O183" s="20"/>
+      <c r="P183" s="20"/>
+      <c r="Q183" s="20"/>
+      <c r="R183" s="20"/>
+      <c r="S183" s="20"/>
+      <c r="T183" s="20"/>
     </row>
     <row r="184" spans="1:20">
-      <c r="A184" s="38"/>
-      <c r="B184" s="38"/>
-      <c r="C184" s="25"/>
-      <c r="D184" s="25"/>
-      <c r="E184" s="25"/>
-      <c r="F184" s="25"/>
-      <c r="G184" s="38"/>
-      <c r="H184" s="25"/>
-      <c r="I184" s="38"/>
-      <c r="J184" s="38"/>
-      <c r="K184" s="38"/>
-      <c r="L184" s="42"/>
-      <c r="M184" s="38"/>
-      <c r="N184" s="38"/>
-      <c r="O184" s="38"/>
-      <c r="P184" s="38"/>
-      <c r="Q184" s="38"/>
-      <c r="R184" s="38"/>
-      <c r="S184" s="38"/>
-      <c r="T184" s="38"/>
+      <c r="A184" s="20"/>
+      <c r="B184" s="20"/>
+      <c r="C184" s="19"/>
+      <c r="D184" s="19"/>
+      <c r="E184" s="19"/>
+      <c r="F184" s="19"/>
+      <c r="G184" s="20"/>
+      <c r="H184" s="19"/>
+      <c r="I184" s="20"/>
+      <c r="J184" s="20"/>
+      <c r="K184" s="20"/>
+      <c r="L184" s="29"/>
+      <c r="M184" s="20"/>
+      <c r="N184" s="20"/>
+      <c r="O184" s="20"/>
+      <c r="P184" s="20"/>
+      <c r="Q184" s="20"/>
+      <c r="R184" s="20"/>
+      <c r="S184" s="20"/>
+      <c r="T184" s="20"/>
     </row>
     <row r="185" spans="1:20">
-      <c r="A185" s="38"/>
-      <c r="B185" s="39"/>
-      <c r="C185" s="25"/>
-      <c r="D185" s="25"/>
-      <c r="E185" s="25"/>
-      <c r="F185" s="25"/>
-      <c r="G185" s="40"/>
-      <c r="H185" s="25"/>
-      <c r="I185" s="40"/>
-      <c r="J185" s="38"/>
-      <c r="K185" s="38"/>
-      <c r="L185" s="42"/>
-      <c r="M185" s="38"/>
-      <c r="N185" s="38"/>
-      <c r="O185" s="38"/>
-      <c r="P185" s="38"/>
-      <c r="Q185" s="38"/>
-      <c r="R185" s="38"/>
-      <c r="S185" s="38"/>
-      <c r="T185" s="38"/>
+      <c r="A185" s="20"/>
+      <c r="B185" s="28"/>
+      <c r="C185" s="19"/>
+      <c r="D185" s="19"/>
+      <c r="E185" s="19"/>
+      <c r="F185" s="19"/>
+      <c r="G185" s="20"/>
+      <c r="H185" s="19"/>
+      <c r="I185" s="20"/>
+      <c r="J185" s="20"/>
+      <c r="K185" s="20"/>
+      <c r="L185" s="29"/>
+      <c r="M185" s="20"/>
+      <c r="N185" s="20"/>
+      <c r="O185" s="20"/>
+      <c r="P185" s="20"/>
+      <c r="Q185" s="20"/>
+      <c r="R185" s="20"/>
+      <c r="S185" s="20"/>
+      <c r="T185" s="20"/>
     </row>
     <row r="186" spans="1:20">
-      <c r="A186" s="38"/>
-      <c r="B186" s="38"/>
-      <c r="C186" s="25"/>
-      <c r="D186" s="25"/>
-      <c r="E186" s="25"/>
-      <c r="F186" s="25"/>
-      <c r="G186" s="38"/>
-      <c r="H186" s="25"/>
-      <c r="I186" s="38"/>
-      <c r="J186" s="38"/>
-      <c r="K186" s="38"/>
-      <c r="L186" s="42"/>
-      <c r="M186" s="38"/>
-      <c r="N186" s="38"/>
-      <c r="O186" s="38"/>
-      <c r="P186" s="38"/>
-      <c r="Q186" s="38"/>
-      <c r="R186" s="38"/>
-      <c r="S186" s="38"/>
-      <c r="T186" s="38"/>
+      <c r="A186" s="20"/>
+      <c r="B186" s="20"/>
+      <c r="C186" s="19"/>
+      <c r="D186" s="19"/>
+      <c r="E186" s="19"/>
+      <c r="F186" s="19"/>
+      <c r="G186" s="20"/>
+      <c r="H186" s="19"/>
+      <c r="I186" s="20"/>
+      <c r="J186" s="20"/>
+      <c r="K186" s="20"/>
+      <c r="L186" s="29"/>
+      <c r="M186" s="20"/>
+      <c r="N186" s="20"/>
+      <c r="O186" s="20"/>
+      <c r="P186" s="20"/>
+      <c r="Q186" s="20"/>
+      <c r="R186" s="20"/>
+      <c r="S186" s="20"/>
+      <c r="T186" s="20"/>
     </row>
     <row r="187" spans="1:20">
-      <c r="A187" s="38"/>
-      <c r="B187" s="38"/>
-      <c r="C187" s="25"/>
-      <c r="D187" s="25"/>
-      <c r="E187" s="25"/>
-      <c r="F187" s="25"/>
-      <c r="G187" s="38"/>
-      <c r="H187" s="25"/>
-      <c r="I187" s="38"/>
-      <c r="J187" s="38"/>
-      <c r="K187" s="38"/>
-      <c r="L187" s="42"/>
-      <c r="M187" s="38"/>
-      <c r="N187" s="38"/>
-      <c r="O187" s="38"/>
-      <c r="P187" s="38"/>
-      <c r="Q187" s="38"/>
-      <c r="R187" s="38"/>
-      <c r="S187" s="38"/>
-      <c r="T187" s="38"/>
+      <c r="A187" s="20"/>
+      <c r="B187" s="20"/>
+      <c r="C187" s="19"/>
+      <c r="D187" s="19"/>
+      <c r="E187" s="19"/>
+      <c r="F187" s="19"/>
+      <c r="G187" s="20"/>
+      <c r="H187" s="19"/>
+      <c r="I187" s="20"/>
+      <c r="J187" s="20"/>
+      <c r="K187" s="20"/>
+      <c r="L187" s="29"/>
+      <c r="M187" s="20"/>
+      <c r="N187" s="20"/>
+      <c r="O187" s="20"/>
+      <c r="P187" s="20"/>
+      <c r="Q187" s="20"/>
+      <c r="R187" s="20"/>
+      <c r="S187" s="20"/>
+      <c r="T187" s="20"/>
     </row>
     <row r="188" spans="1:20">
-      <c r="A188" s="38"/>
-      <c r="B188" s="38"/>
-      <c r="C188" s="38"/>
-      <c r="D188" s="38"/>
-      <c r="E188" s="38"/>
-      <c r="F188" s="38"/>
-      <c r="G188" s="38"/>
-      <c r="H188" s="38"/>
-      <c r="I188" s="38"/>
-      <c r="J188" s="38"/>
-      <c r="K188" s="38"/>
-      <c r="L188" s="38"/>
-      <c r="M188" s="38"/>
-      <c r="N188" s="38"/>
-      <c r="O188" s="38"/>
-      <c r="P188" s="38"/>
-      <c r="Q188" s="38"/>
-      <c r="R188" s="38"/>
-      <c r="S188" s="38"/>
-      <c r="T188" s="38"/>
+      <c r="A188" s="20"/>
+      <c r="B188" s="20"/>
+      <c r="C188" s="20"/>
+      <c r="D188" s="20"/>
+      <c r="E188" s="20"/>
+      <c r="F188" s="20"/>
+      <c r="G188" s="20"/>
+      <c r="H188" s="20"/>
+      <c r="I188" s="20"/>
+      <c r="J188" s="20"/>
+      <c r="K188" s="20"/>
+      <c r="L188" s="20"/>
+      <c r="M188" s="20"/>
+      <c r="N188" s="20"/>
+      <c r="O188" s="20"/>
+      <c r="P188" s="20"/>
+      <c r="Q188" s="20"/>
+      <c r="R188" s="20"/>
+      <c r="S188" s="20"/>
+      <c r="T188" s="20"/>
     </row>
     <row r="194" spans="1:20">
-      <c r="A194" s="38"/>
-      <c r="B194" s="38"/>
-      <c r="C194" s="38"/>
-      <c r="D194" s="38"/>
-      <c r="E194" s="38"/>
-      <c r="F194" s="38"/>
-      <c r="G194" s="38"/>
-      <c r="H194" s="38"/>
-      <c r="I194" s="38"/>
-      <c r="J194" s="38"/>
-      <c r="K194" s="38"/>
-      <c r="L194" s="38"/>
-      <c r="M194" s="38"/>
-      <c r="N194" s="38"/>
-      <c r="O194" s="38"/>
-      <c r="P194" s="38"/>
-      <c r="Q194" s="38"/>
-      <c r="R194" s="38"/>
-      <c r="S194" s="38"/>
-      <c r="T194" s="38"/>
+      <c r="A194" s="20"/>
+      <c r="B194" s="20"/>
+      <c r="C194" s="20"/>
+      <c r="D194" s="20"/>
+      <c r="E194" s="20"/>
+      <c r="F194" s="20"/>
+      <c r="G194" s="20"/>
+      <c r="H194" s="20"/>
+      <c r="I194" s="20"/>
+      <c r="J194" s="20"/>
+      <c r="K194" s="20"/>
+      <c r="L194" s="20"/>
+      <c r="M194" s="20"/>
+      <c r="N194" s="20"/>
+      <c r="O194" s="20"/>
+      <c r="P194" s="20"/>
+      <c r="Q194" s="20"/>
+      <c r="R194" s="20"/>
+      <c r="S194" s="20"/>
+      <c r="T194" s="20"/>
     </row>
     <row r="195" spans="1:20">
-      <c r="A195" s="38"/>
-      <c r="B195" s="38"/>
-      <c r="C195" s="38"/>
-      <c r="D195" s="38"/>
-      <c r="E195" s="38"/>
-      <c r="F195" s="38"/>
-      <c r="G195" s="38"/>
-      <c r="H195" s="38"/>
-      <c r="I195" s="38"/>
-      <c r="J195" s="38"/>
-      <c r="K195" s="38"/>
-      <c r="L195" s="38"/>
-      <c r="M195" s="38"/>
-      <c r="N195" s="38"/>
-      <c r="O195" s="38"/>
-      <c r="P195" s="38"/>
-      <c r="Q195" s="38"/>
-      <c r="R195" s="38"/>
-      <c r="S195" s="38"/>
-      <c r="T195" s="38"/>
+      <c r="A195" s="20"/>
+      <c r="B195" s="20"/>
+      <c r="C195" s="20"/>
+      <c r="D195" s="20"/>
+      <c r="E195" s="20"/>
+      <c r="F195" s="20"/>
+      <c r="G195" s="20"/>
+      <c r="H195" s="20"/>
+      <c r="I195" s="20"/>
+      <c r="J195" s="20"/>
+      <c r="K195" s="20"/>
+      <c r="L195" s="20"/>
+      <c r="M195" s="20"/>
+      <c r="N195" s="20"/>
+      <c r="O195" s="20"/>
+      <c r="P195" s="20"/>
+      <c r="Q195" s="20"/>
+      <c r="R195" s="20"/>
+      <c r="S195" s="20"/>
+      <c r="T195" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
